--- a/tests/Metrado.Excel.Tests/Goldens/material-layers.xlsx
+++ b/tests/Metrado.Excel.Tests/Goldens/material-layers.xlsx
@@ -95,13 +95,10 @@
     <x:t>walls-03</x:t>
   </x:si>
   <x:si>
-    <x:t>Finish1 15 mm</x:t>
-  </x:si>
-  <x:si>
     <x:t>Tarrajeo impermeabilizado 1:4</x:t>
   </x:si>
   <x:si>
-    <x:t>Finish2 20 mm</x:t>
+    <x:t>Finish1 20 mm</x:t>
   </x:si>
   <x:si>
     <x:t>02.05.01</x:t>
@@ -113,7 +110,7 @@
     <x:t>Finish1 10 mm</x:t>
   </x:si>
   <x:si>
-    <x:t>Unclassified elements</x:t>
+    <x:t>Unclassified lines</x:t>
   </x:si>
   <x:si>
     <x:t>Count</x:t>
@@ -137,10 +134,10 @@
     <x:t>Generic - 200mm</x:t>
   </x:si>
   <x:si>
+    <x:t>Sheathing</x:t>
+  </x:si>
+  <x:si>
     <x:t>Air</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Metal Stud Layer</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -718,10 +715,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -747,10 +744,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -761,7 +758,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E12" s="0">
         <x:v>13.11</x:v>
@@ -778,7 +775,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
         <x:v>16</x:v>
@@ -793,10 +790,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I13" s="0" t="s">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="I13" s="0" t="s">
-        <x:v>31</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -818,12 +815,12 @@
   <x:sheetData>
     <x:row r="1" spans="1:5">
       <x:c r="A1" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B2" s="0">
         <x:v>2</x:v>
@@ -834,13 +831,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C3" s="0" t="s">
+      <x:c r="D3" s="0" t="s">
         <x:v>35</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>36</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
         <x:v>8</x:v>
@@ -848,36 +845,36 @@
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
+      <x:c r="D4" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="D4" s="0" t="s">
+      <x:c r="E4" s="0" t="s">
         <x:v>39</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
+      <x:c r="D5" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/tests/Metrado.Excel.Tests/Goldens/material-layers.xlsx
+++ b/tests/Metrado.Excel.Tests/Goldens/material-layers.xlsx
@@ -98,7 +98,7 @@
     <x:t>Tarrajeo impermeabilizado 1:4</x:t>
   </x:si>
   <x:si>
-    <x:t>Finish1 20 mm</x:t>
+    <x:t>Finish1 15 mm</x:t>
   </x:si>
   <x:si>
     <x:t>02.05.01</x:t>
